--- a/nr-rm-adeli/ig/StructureDefinition-fr-core-observation-resp-rate.xlsx
+++ b/nr-rm-adeli/ig/StructureDefinition-fr-core-observation-resp-rate.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-10-06T10:53:29+00:00</t>
+    <t>2024-10-29T10:41:10+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -87,7 +87,7 @@
     <t>Description</t>
   </si>
   <si>
-    <t>Profile of the ObservationResprate profil (described in the HL7 VitalSigns profil) for France.
+    <t>French profile for the ObservationResprate profil (described in the HL7 VitalSigns profil) for France.
 Profilage du profil ObservationResprate (décrit dans le profil HL7 VitaSigns) pour l'usage en France</t>
   </si>
   <si>
